--- a/CardFiles/Forms.xlsx
+++ b/CardFiles/Forms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\CardFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BB5885-304E-43BE-8C1F-7655911CF530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0193FD9C-DC0E-4F85-9E37-E4FC6F96B1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
